--- a/data/dividends_info_20260323.xlsx
+++ b/data/dividends_info_20260323.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>50.34999847412109</v>
+        <v>50.54999923706055</v>
       </c>
       <c r="I2" t="n">
-        <v>1.390268165270722</v>
+        <v>1.384767577774358</v>
       </c>
       <c r="J2" t="n">
         <v>336</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.96399998664856</v>
+        <v>1.960000038146973</v>
       </c>
       <c r="I3" t="n">
-        <v>3.920570291418157</v>
+        <v>3.928571352110661</v>
       </c>
       <c r="J3" t="n">
         <v>245</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5.389999866485596</v>
+        <v>5.449999809265137</v>
       </c>
       <c r="I4" t="n">
-        <v>3.710575231060341</v>
+        <v>3.669724899072381</v>
       </c>
       <c r="J4" t="n">
         <v>238</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>9.135000228881836</v>
+        <v>9.067000389099121</v>
       </c>
       <c r="I5" t="n">
-        <v>2.846195878331414</v>
+        <v>2.867541511441725</v>
       </c>
       <c r="J5" t="n">
         <v>119</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>18.29999923706055</v>
+        <v>18.39999961853027</v>
       </c>
       <c r="I6" t="n">
-        <v>2.054644894402713</v>
+        <v>2.04347830323506</v>
       </c>
       <c r="J6" t="n">
         <v>119</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4.244999885559082</v>
+        <v>4.414999961853027</v>
       </c>
       <c r="I7" t="n">
-        <v>2.826855199884077</v>
+        <v>2.718006818501411</v>
       </c>
       <c r="J7" t="n">
         <v>112</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.119999885559082</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I8" t="n">
-        <v>4.009434178699683</v>
+        <v>4.047619231433834</v>
       </c>
       <c r="J8" t="n">
         <v>105</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>30.60000038146973</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4901960723204261</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>105</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>20.10000038146973</v>
+        <v>20.70000076293945</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9701492353192755</v>
+        <v>0.9420289507869057</v>
       </c>
       <c r="J11" t="n">
         <v>91</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>60.59999847412109</v>
+        <v>59.20000076293945</v>
       </c>
       <c r="I12" t="n">
-        <v>1.039603986572769</v>
+        <v>1.064189175474461</v>
       </c>
       <c r="J12" t="n">
         <v>91</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>21.45000076293945</v>
+        <v>19.97999954223633</v>
       </c>
       <c r="I13" t="n">
-        <v>3.962703821757432</v>
+        <v>4.254254351723878</v>
       </c>
       <c r="J13" t="n">
         <v>91</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6.369999885559082</v>
+        <v>6.254000186920166</v>
       </c>
       <c r="I14" t="n">
-        <v>2.846153897286729</v>
+        <v>2.898944588763798</v>
       </c>
       <c r="J14" t="n">
         <v>91</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7.690000057220459</v>
+        <v>7.75</v>
       </c>
       <c r="I15" t="n">
-        <v>3.381014279133526</v>
+        <v>3.354838709677419</v>
       </c>
       <c r="J15" t="n">
         <v>91</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>25.45000076293945</v>
+        <v>25.75</v>
       </c>
       <c r="I16" t="n">
-        <v>4.361492993023377</v>
+        <v>4.310679611650485</v>
       </c>
       <c r="J16" t="n">
         <v>73</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.8159999847412109</v>
+        <v>0.8199999928474426</v>
       </c>
       <c r="I17" t="n">
-        <v>3.676470656983444</v>
+        <v>3.658536617277918</v>
       </c>
       <c r="J17" t="n">
         <v>70</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.4659999907016754</v>
+        <v>0.4600000083446503</v>
       </c>
       <c r="I18" t="n">
-        <v>4.935622416079441</v>
+        <v>4.999999909297282</v>
       </c>
       <c r="J18" t="n">
         <v>70</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>11.5</v>
+        <v>11.77000045776367</v>
       </c>
       <c r="I19" t="n">
-        <v>2.173913043478261</v>
+        <v>2.124044097509751</v>
       </c>
       <c r="J19" t="n">
         <v>63</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3.539999961853027</v>
+        <v>3.5</v>
       </c>
       <c r="I20" t="n">
-        <v>4.237288181254157</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="J20" t="n">
         <v>63</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2.339999914169312</v>
+        <v>2.305000066757202</v>
       </c>
       <c r="I21" t="n">
-        <v>4.444444607465701</v>
+        <v>4.511930455009174</v>
       </c>
       <c r="J21" t="n">
         <v>56</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>8.369999885559082</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="I22" t="n">
-        <v>3.464755125031034</v>
+        <v>3.452381109164151</v>
       </c>
       <c r="J22" t="n">
         <v>56</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.96399998664856</v>
+        <v>1.960000038146973</v>
       </c>
       <c r="I23" t="n">
-        <v>3.920570291418157</v>
+        <v>3.928571352110661</v>
       </c>
       <c r="J23" t="n">
         <v>56</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>33.34999847412109</v>
+        <v>33.34000015258789</v>
       </c>
       <c r="I24" t="n">
-        <v>4.917541454379993</v>
+        <v>4.919016174247681</v>
       </c>
       <c r="J24" t="n">
         <v>56</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>31.68000030517578</v>
+        <v>32.38000106811523</v>
       </c>
       <c r="I25" t="n">
-        <v>6.313131252316453</v>
+        <v>6.176652050729581</v>
       </c>
       <c r="J25" t="n">
         <v>56</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>3.579999923706055</v>
+        <v>3.638000011444092</v>
       </c>
       <c r="I26" t="n">
-        <v>2.79329614891385</v>
+        <v>2.748763047977708</v>
       </c>
       <c r="J26" t="n">
         <v>56</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>35</v>
+        <v>34.79999923706055</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4241714285714286</v>
+        <v>0.4266092047550861</v>
       </c>
       <c r="J27" t="n">
         <v>56</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>21.79999923706055</v>
+        <v>22.23999977111816</v>
       </c>
       <c r="I28" t="n">
-        <v>4.220183633933238</v>
+        <v>4.136690690054558</v>
       </c>
       <c r="J28" t="n">
         <v>56</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>7.474999904632568</v>
+        <v>7.639999866485596</v>
       </c>
       <c r="I29" t="n">
-        <v>4.013377977624823</v>
+        <v>3.926701639302517</v>
       </c>
       <c r="J29" t="n">
         <v>56</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>72.33999633789062</v>
+        <v>73.81999969482422</v>
       </c>
       <c r="I30" t="n">
-        <v>1.437655588399945</v>
+        <v>1.408832300595252</v>
       </c>
       <c r="J30" t="n">
         <v>56</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>50.34999847412109</v>
+        <v>50.54999923706055</v>
       </c>
       <c r="I31" t="n">
-        <v>4.369414233707984</v>
+        <v>4.352126673005126</v>
       </c>
       <c r="J31" t="n">
         <v>56</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>7.065000057220459</v>
+        <v>7.254000186920166</v>
       </c>
       <c r="I32" t="n">
-        <v>12.17268213778819</v>
+        <v>11.85552767906849</v>
       </c>
       <c r="J32" t="n">
         <v>56</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>10.46500015258789</v>
+        <v>10.83500003814697</v>
       </c>
       <c r="I33" t="n">
-        <v>5.35117049053762</v>
+        <v>5.168435607091816</v>
       </c>
       <c r="J33" t="n">
         <v>56</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.754999995231628</v>
+        <v>1.759999990463257</v>
       </c>
       <c r="I34" t="n">
-        <v>2.279202285394919</v>
+        <v>2.272727285042282</v>
       </c>
       <c r="J34" t="n">
         <v>56</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>8.720000267028809</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="I35" t="n">
-        <v>3.440366867124189</v>
+        <v>3.448275937667407</v>
       </c>
       <c r="J35" t="n">
         <v>56</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>60.70000076293945</v>
+        <v>61.90000152587891</v>
       </c>
       <c r="I37" t="n">
-        <v>3.393739660803659</v>
+        <v>3.327948221679386</v>
       </c>
       <c r="J37" t="n">
         <v>56</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>14.07999992370605</v>
+        <v>14.35999965667725</v>
       </c>
       <c r="I38" t="n">
-        <v>5.326704574317849</v>
+        <v>5.222841350495841</v>
       </c>
       <c r="J38" t="n">
         <v>56</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>14.26000022888184</v>
+        <v>15.11999988555908</v>
       </c>
       <c r="I39" t="n">
-        <v>2.103786782502203</v>
+        <v>1.984126999144531</v>
       </c>
       <c r="J39" t="n">
         <v>56</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>39.29999923706055</v>
+        <v>41</v>
       </c>
       <c r="I40" t="n">
-        <v>2.162849914761413</v>
+        <v>2.073170731707317</v>
       </c>
       <c r="J40" t="n">
         <v>56</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>29.44000053405762</v>
+        <v>30</v>
       </c>
       <c r="I41" t="n">
-        <v>2.887228208493675</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="J41" t="n">
         <v>56</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>5.389999866485596</v>
+        <v>5.449999809265137</v>
       </c>
       <c r="I42" t="n">
-        <v>3.710575231060341</v>
+        <v>3.669724899072381</v>
       </c>
       <c r="J42" t="n">
         <v>56</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>22.20000076293945</v>
+        <v>20.63999938964844</v>
       </c>
       <c r="I43" t="n">
-        <v>4.504504349699816</v>
+        <v>4.844961383581868</v>
       </c>
       <c r="J43" t="n">
         <v>56</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>4.300000190734863</v>
+        <v>4.239999771118164</v>
       </c>
       <c r="I44" t="n">
-        <v>4.999999778215285</v>
+        <v>5.070754990708423</v>
       </c>
       <c r="J44" t="n">
         <v>56</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>18.23500061035156</v>
+        <v>18.52000045776367</v>
       </c>
       <c r="I45" t="n">
-        <v>4.332327795764023</v>
+        <v>4.265658641864819</v>
       </c>
       <c r="J45" t="n">
         <v>56</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>4.570000171661377</v>
+        <v>4.550000190734863</v>
       </c>
       <c r="I46" t="n">
-        <v>2.035010864478607</v>
+        <v>2.043955958273921</v>
       </c>
       <c r="J46" t="n">
         <v>56</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>30.97999954223633</v>
+        <v>32.02000045776367</v>
       </c>
       <c r="I47" t="n">
-        <v>1.129761152910381</v>
+        <v>1.093066817602552</v>
       </c>
       <c r="J47" t="n">
         <v>56</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>11.44999980926514</v>
+        <v>11.35000038146973</v>
       </c>
       <c r="I49" t="n">
-        <v>1.746724919926754</v>
+        <v>1.762114478220852</v>
       </c>
       <c r="J49" t="n">
         <v>56</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>5.429999828338623</v>
+        <v>5.599999904632568</v>
       </c>
       <c r="I50" t="n">
-        <v>1.896869304902246</v>
+        <v>1.839285745608564</v>
       </c>
       <c r="J50" t="n">
         <v>56</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>4.966000080108643</v>
+        <v>5.123000144958496</v>
       </c>
       <c r="I51" t="n">
-        <v>3.826016853303058</v>
+        <v>3.708764290919989</v>
       </c>
       <c r="J51" t="n">
         <v>56</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>9.725000381469727</v>
+        <v>9.694999694824219</v>
       </c>
       <c r="I52" t="n">
-        <v>4.442159208786708</v>
+        <v>4.45590524598601</v>
       </c>
       <c r="J52" t="n">
         <v>56</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>6.510000228881836</v>
+        <v>6.78000020980835</v>
       </c>
       <c r="I54" t="n">
-        <v>7.219661804539254</v>
+        <v>6.932153177813626</v>
       </c>
       <c r="J54" t="n">
         <v>56</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2.844000101089478</v>
+        <v>2.900000095367432</v>
       </c>
       <c r="I56" t="n">
-        <v>10.54852283180567</v>
+        <v>10.34482724601393</v>
       </c>
       <c r="J56" t="n">
         <v>56</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>44.68000030517578</v>
+        <v>45.22000122070312</v>
       </c>
       <c r="I57" t="n">
-        <v>1.589077876344045</v>
+        <v>1.570101682515966</v>
       </c>
       <c r="J57" t="n">
         <v>56</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>78.75</v>
+        <v>78.34999847412109</v>
       </c>
       <c r="I58" t="n">
-        <v>1.714285714285714</v>
+        <v>1.723037685119934</v>
       </c>
       <c r="J58" t="n">
         <v>56</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>3.420000076293945</v>
+        <v>3.480000019073486</v>
       </c>
       <c r="I59" t="n">
-        <v>4.970760123029561</v>
+        <v>4.885057444489921</v>
       </c>
       <c r="J59" t="n">
         <v>56</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>4.380000114440918</v>
+        <v>4.650000095367432</v>
       </c>
       <c r="I60" t="n">
-        <v>0.9132419852711756</v>
+        <v>0.8602150361211831</v>
       </c>
       <c r="J60" t="n">
         <v>56</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>28.89999961853027</v>
+        <v>29.89999961853027</v>
       </c>
       <c r="I61" t="n">
-        <v>3.633218041036772</v>
+        <v>3.51170573042172</v>
       </c>
       <c r="J61" t="n">
         <v>56</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>17.22999954223633</v>
+        <v>17.44000053405762</v>
       </c>
       <c r="I62" t="n">
-        <v>2.205455659290626</v>
+        <v>2.17889901584532</v>
       </c>
       <c r="J62" t="n">
         <v>56</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>24.48999977111816</v>
+        <v>24.32999992370605</v>
       </c>
       <c r="I63" t="n">
-        <v>2.449979606400809</v>
+        <v>2.466091253109241</v>
       </c>
       <c r="J63" t="n">
         <v>56</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>30.85000038146973</v>
+        <v>30</v>
       </c>
       <c r="I64" t="n">
-        <v>1.134521866036118</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="J64" t="n">
         <v>56</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2.236000061035156</v>
+        <v>2.308000087738037</v>
       </c>
       <c r="I65" t="n">
-        <v>11.62790665934208</v>
+        <v>11.26516421647167</v>
       </c>
       <c r="J65" t="n">
         <v>56</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>9.939999580383301</v>
+        <v>9.560000419616699</v>
       </c>
       <c r="I66" t="n">
-        <v>3.521126909207611</v>
+        <v>3.66108770541281</v>
       </c>
       <c r="J66" t="n">
         <v>49</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>4.860000133514404</v>
+        <v>4.760000228881836</v>
       </c>
       <c r="I67" t="n">
-        <v>1.975308587709434</v>
+        <v>2.0168066257121</v>
       </c>
       <c r="J67" t="n">
         <v>49</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>13.92000007629395</v>
+        <v>14.18000030517578</v>
       </c>
       <c r="I68" t="n">
-        <v>3.591954003301412</v>
+        <v>3.526093012970508</v>
       </c>
       <c r="J68" t="n">
         <v>49</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>6.489999771118164</v>
+        <v>6.650000095367432</v>
       </c>
       <c r="I69" t="n">
-        <v>3.389830628023214</v>
+        <v>3.308270629247929</v>
       </c>
       <c r="J69" t="n">
         <v>49</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3.365000009536743</v>
+        <v>3.349999904632568</v>
       </c>
       <c r="I70" t="n">
-        <v>4.754829109852724</v>
+        <v>4.776119538951121</v>
       </c>
       <c r="J70" t="n">
         <v>42</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>19.31999969482422</v>
+        <v>18.52000045776367</v>
       </c>
       <c r="I71" t="n">
-        <v>3.157349946353351</v>
+        <v>3.293736419667771</v>
       </c>
       <c r="J71" t="n">
         <v>42</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>11.85000038146973</v>
+        <v>11.94999980926514</v>
       </c>
       <c r="I72" t="n">
-        <v>5.907172805619612</v>
+        <v>5.857740679269905</v>
       </c>
       <c r="J72" t="n">
         <v>42</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>8.409999847412109</v>
+        <v>8.670000076293945</v>
       </c>
       <c r="I73" t="n">
-        <v>6.070154688018085</v>
+        <v>5.888119902049838</v>
       </c>
       <c r="J73" t="n">
         <v>42</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>6.945000171661377</v>
+        <v>7.5</v>
       </c>
       <c r="I74" t="n">
-        <v>3.887688888788189</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="J74" t="n">
         <v>42</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>4.53000020980835</v>
+        <v>4.730000019073486</v>
       </c>
       <c r="I75" t="n">
-        <v>7.726268957828755</v>
+        <v>7.399577137180606</v>
       </c>
       <c r="J75" t="n">
         <v>42</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>18.5</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="I76" t="n">
-        <v>4.054054054054054</v>
+        <v>4.032257981818046</v>
       </c>
       <c r="J76" t="n">
         <v>42</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>10.30000019073486</v>
+        <v>10.19999980926514</v>
       </c>
       <c r="I77" t="n">
-        <v>4.174757204245461</v>
+        <v>4.215686353341016</v>
       </c>
       <c r="J77" t="n">
         <v>42</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>3.904999971389771</v>
+        <v>3.924999952316284</v>
       </c>
       <c r="I78" t="n">
-        <v>3.841229221484878</v>
+        <v>3.821656097383634</v>
       </c>
       <c r="J78" t="n">
         <v>42</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>11.53999996185303</v>
+        <v>11.73999977111816</v>
       </c>
       <c r="I79" t="n">
-        <v>1.708570196289149</v>
+        <v>1.679463405826122</v>
       </c>
       <c r="J79" t="n">
         <v>42</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>25</v>
+        <v>25.60000038146973</v>
       </c>
       <c r="I80" t="n">
-        <v>4.4</v>
+        <v>4.296874935971575</v>
       </c>
       <c r="J80" t="n">
         <v>42</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>36</v>
+        <v>36.65000152587891</v>
       </c>
       <c r="I81" t="n">
-        <v>1.305555555555555</v>
+        <v>1.282401038013951</v>
       </c>
       <c r="J81" t="n">
         <v>42</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>75.40000152587891</v>
+        <v>75.80000305175781</v>
       </c>
       <c r="I82" t="n">
-        <v>1.591511904131904</v>
+        <v>1.583113392727194</v>
       </c>
       <c r="J82" t="n">
         <v>42</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>22.14999961853027</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="I83" t="n">
-        <v>1.218961646275258</v>
+        <v>1.179039320950559</v>
       </c>
       <c r="J83" t="n">
         <v>42</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>27.39999961853027</v>
+        <v>27.85000038146973</v>
       </c>
       <c r="I85" t="n">
-        <v>1.094890526192248</v>
+        <v>1.077199267112427</v>
       </c>
       <c r="J85" t="n">
         <v>42</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>5.909999847412109</v>
+        <v>6.190000057220459</v>
       </c>
       <c r="I86" t="n">
-        <v>2.707275873620561</v>
+        <v>2.584814192584127</v>
       </c>
       <c r="J86" t="n">
         <v>35</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>2.140000104904175</v>
+        <v>2.154999971389771</v>
       </c>
       <c r="I87" t="n">
-        <v>3.037383028675626</v>
+        <v>3.016241339348193</v>
       </c>
       <c r="J87" t="n">
         <v>35</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>7.329999923706055</v>
+        <v>7.429999828338623</v>
       </c>
       <c r="I88" t="n">
-        <v>3.410641236045195</v>
+        <v>3.364737628209353</v>
       </c>
       <c r="J88" t="n">
         <v>35</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1.340000033378601</v>
+        <v>1.320000052452087</v>
       </c>
       <c r="I89" t="n">
-        <v>5.223880466891178</v>
+        <v>5.30303009230682</v>
       </c>
       <c r="J89" t="n">
         <v>35</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>6.585000038146973</v>
+        <v>6.574999809265137</v>
       </c>
       <c r="I90" t="n">
-        <v>7.593014382741001</v>
+        <v>7.604562958244149</v>
       </c>
       <c r="J90" t="n">
         <v>28</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>16.44000053405762</v>
+        <v>16.75</v>
       </c>
       <c r="I91" t="n">
-        <v>3.953771161098443</v>
+        <v>3.880597014925373</v>
       </c>
       <c r="J91" t="n">
         <v>28</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>11.24499988555908</v>
+        <v>11.65999984741211</v>
       </c>
       <c r="I92" t="n">
-        <v>4.802134330774625</v>
+        <v>4.631217899371165</v>
       </c>
       <c r="J92" t="n">
         <v>28</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>8.159999847412109</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="I94" t="n">
-        <v>1.96078435039117</v>
+        <v>1.95121955758117</v>
       </c>
       <c r="J94" t="n">
         <v>28</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>273.7999877929688</v>
+        <v>283.1000061035156</v>
       </c>
       <c r="I95" t="n">
-        <v>1.320306852143999</v>
+        <v>1.276933918072108</v>
       </c>
       <c r="J95" t="n">
         <v>28</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>12.14999961853027</v>
+        <v>12.84000015258789</v>
       </c>
       <c r="I97" t="n">
-        <v>4.814814965984045</v>
+        <v>4.556074712211696</v>
       </c>
       <c r="J97" t="n">
         <v>28</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>15.625</v>
+        <v>16.04999923706055</v>
       </c>
       <c r="I98" t="n">
-        <v>4.032</v>
+        <v>3.925233831446465</v>
       </c>
       <c r="J98" t="n">
         <v>28</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>93.90000152587891</v>
+        <v>94.90000152587891</v>
       </c>
       <c r="I99" t="n">
-        <v>0.9584664380990019</v>
+        <v>0.9483666865427531</v>
       </c>
       <c r="J99" t="n">
         <v>28</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>59.63000106811523</v>
+        <v>61.61999893188477</v>
       </c>
       <c r="I100" t="n">
-        <v>2.885795688707658</v>
+        <v>2.792599853664694</v>
       </c>
       <c r="J100" t="n">
         <v>28</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>22.79999923706055</v>
+        <v>22.39999961853027</v>
       </c>
       <c r="I101" t="n">
-        <v>0.6140351082662987</v>
+        <v>0.6250000106436868</v>
       </c>
       <c r="J101" t="n">
         <v>21</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>1.450000047683716</v>
+        <v>1.470000028610229</v>
       </c>
       <c r="I102" t="n">
-        <v>4.137930898405571</v>
+        <v>4.081632573621466</v>
       </c>
       <c r="J102" t="n">
         <v>21</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>1.929999947547913</v>
+        <v>1.894999980926514</v>
       </c>
       <c r="I103" t="n">
-        <v>1.7616580789651</v>
+        <v>1.794195268718501</v>
       </c>
       <c r="J103" t="n">
         <v>7</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>23.36000061035156</v>
+        <v>22.52000045776367</v>
       </c>
       <c r="I104" t="n">
-        <v>1.113013669549245</v>
+        <v>1.154529283814318</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>26.82999992370605</v>
+        <v>27</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3354453978975942</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>50.34999847412109</v>
+        <v>50.54999923706055</v>
       </c>
       <c r="I106" t="n">
-        <v>1.290963296322813</v>
+        <v>1.285855607933333</v>
       </c>
       <c r="J106" t="n">
         <v>-28</v>
@@ -5434,7 +5434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C317"/>
+  <dimension ref="A1:C307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6562,7 +6562,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6579,7 +6579,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6596,7 +6596,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6613,7 +6613,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6732,7 +6732,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6776,14 +6776,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6800,7 +6800,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6817,7 +6817,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6834,7 +6834,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6844,14 +6844,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6861,14 +6861,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6919,7 +6919,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6987,7 +6987,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7021,7 +7021,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7038,7 +7038,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7055,7 +7055,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7072,7 +7072,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7089,7 +7089,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7106,7 +7106,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7123,7 +7123,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7140,7 +7140,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7157,7 +7157,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7167,14 +7167,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7191,7 +7191,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7208,7 +7208,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7225,7 +7225,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7242,7 +7242,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7252,14 +7252,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7276,7 +7276,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7293,7 +7293,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7310,7 +7310,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7327,7 +7327,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7344,7 +7344,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7361,7 +7361,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7378,7 +7378,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7395,7 +7395,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7412,7 +7412,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7429,7 +7429,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7446,7 +7446,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7463,7 +7463,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7480,7 +7480,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7497,12 +7497,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7514,12 +7514,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7531,12 +7531,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7548,12 +7548,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7565,12 +7565,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7582,12 +7582,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7599,12 +7599,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7616,7 +7616,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7633,7 +7633,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7650,7 +7650,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7667,7 +7667,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7684,7 +7684,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7701,7 +7701,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7718,7 +7718,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7735,7 +7735,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7752,7 +7752,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7769,7 +7769,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7786,7 +7786,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7803,7 +7803,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>HEALTH ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7820,7 +7820,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7837,7 +7837,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7854,7 +7854,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -7864,14 +7864,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -7888,7 +7888,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -7905,7 +7905,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -7922,7 +7922,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -7939,7 +7939,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -7956,7 +7956,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7973,7 +7973,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -7990,7 +7990,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -8007,7 +8007,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -8017,14 +8017,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -8041,7 +8041,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -8058,7 +8058,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -8075,7 +8075,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -8092,7 +8092,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -8126,7 +8126,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -8143,7 +8143,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -8160,46 +8160,46 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -8211,29 +8211,29 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -8245,12 +8245,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -8262,12 +8262,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -8279,12 +8279,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -8296,12 +8296,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -8313,12 +8313,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -8330,7 +8330,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -8340,14 +8340,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -8364,7 +8364,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -8381,7 +8381,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -8398,7 +8398,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -8408,14 +8408,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8425,14 +8425,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8449,7 +8449,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8459,14 +8459,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8483,7 +8483,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8500,7 +8500,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8517,7 +8517,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8534,7 +8534,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8551,7 +8551,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8568,7 +8568,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8578,14 +8578,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8595,14 +8595,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8619,7 +8619,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8636,7 +8636,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -8653,7 +8653,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8670,7 +8670,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8687,7 +8687,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8704,7 +8704,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8714,14 +8714,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8731,14 +8731,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8755,7 +8755,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8772,7 +8772,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8789,63 +8789,63 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -8857,12 +8857,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -8874,80 +8874,80 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -8959,12 +8959,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -8976,267 +8976,267 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -9248,46 +9248,46 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -9299,12 +9299,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -9316,29 +9316,29 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -9350,51 +9350,51 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9418,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -9428,14 +9428,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -9445,14 +9445,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -9462,14 +9462,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -9479,14 +9479,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -9496,14 +9496,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -9513,14 +9513,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -9530,14 +9530,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -9547,104 +9547,104 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9656,12 +9656,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9673,29 +9673,29 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9707,12 +9707,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9724,7 +9724,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9758,7 +9758,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -9768,14 +9768,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -9792,7 +9792,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -9802,14 +9802,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -9819,14 +9819,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -9836,14 +9836,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -9860,7 +9860,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -9870,14 +9870,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -9887,70 +9887,70 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9962,29 +9962,29 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9996,46 +9996,46 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -10047,29 +10047,29 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -10081,12 +10081,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -10098,29 +10098,29 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -10132,29 +10132,29 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -10166,12 +10166,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -10183,109 +10183,109 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -10295,19 +10295,19 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -10319,29 +10319,29 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -10353,29 +10353,29 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -10387,12 +10387,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -10404,29 +10404,29 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -10438,12 +10438,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -10455,12 +10455,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -10472,7 +10472,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -10482,14 +10482,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -10506,7 +10506,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -10523,7 +10523,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -10533,14 +10533,14 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -10557,7 +10557,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -10567,14 +10567,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -10591,7 +10591,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -10601,14 +10601,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -10625,7 +10625,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -10635,14 +10635,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -10651,176 +10651,6 @@
         </is>
       </c>
       <c r="C307" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>E.P.H. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>EQUITA GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>Nusco S.p.A.</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>Tinexta S.p.A.</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>Sicily by Car S.p.A.</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>Racing Force S.p.A.</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>SYS-DAT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>ITALMOBILIARE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
         <is>
           <t>Annual General Meeting</t>
         </is>
@@ -10837,314 +10667,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ENEL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0003128367</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-07-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>9.135000228881836</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2.846195878331414</v>
-      </c>
-      <c r="I2" t="n">
-        <v>119</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ecomembrane S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0005543332</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-05-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>4.860000133514404</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1.975308587709434</v>
-      </c>
-      <c r="I3" t="n">
-        <v>49</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>FNM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IT0000060886</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-06-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0.4659999907016754</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>4.935622416079441</v>
-      </c>
-      <c r="I4" t="n">
-        <v>70</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IT0001078911</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>30.97999954223633</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1.129761152910381</v>
-      </c>
-      <c r="I5" t="n">
-        <v>56</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>IT0003411417</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>11.44999980926514</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1.746724919926754</v>
-      </c>
-      <c r="I6" t="n">
-        <v>56</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RECORDATI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>IT0003828271</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>44.68000030517578</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1.589077876344045</v>
-      </c>
-      <c r="I7" t="n">
-        <v>56</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11155,401 +10680,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ASCOPIAVE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>E.P.H. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>EQUITA GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ERG S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ESAUTOMOTION S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EXPERT.AI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Annual Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Ecomembrane S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Fiera Milano S.p.A</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Friends S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>GEOX S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Gismondi 1754 S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ITALMOBILIARE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Kruso Kapital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Nusco S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Racing Force S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SAIPEM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SYS-DAT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sicily by Car S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Tinexta S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>